--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
         <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -179,6 +184,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,7 +595,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  5 overs  |  2 unders  |  8.5 recommended units at risk</t>
+          <t>7 bets today  |  5 overs  |  2 unders  |  9.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -636,21 +659,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -658,42 +681,42 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.676</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1522</v>
+        <v>0.178</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -704,39 +727,39 @@
         <v>-108</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.655</v>
+        <v>0.672</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>0.5192</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1358</v>
+        <v>0.1528</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
@@ -744,108 +767,108 @@
         </is>
       </c>
       <c r="F6" s="17" t="n">
-        <v>116</v>
+        <v>-120</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.569</v>
+        <v>0.66</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.463</v>
+        <v>0.5455</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.106</v>
+        <v>0.1145</v>
       </c>
       <c r="J6" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" s="21" t="n">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Erick Fedde</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>134</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.4274</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>0.09959999999999999</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.44</v>
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>116</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="J7" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>0.0868</v>
-      </c>
-      <c r="J8" s="18" t="n">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Erick Fedde</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="J8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="21" t="n">
-        <v>0.5</v>
+      <c r="K8" s="9" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -873,22 +896,22 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.523</v>
+        <v>0.517</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0.4425</v>
+        <v>0.4545</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0.0805</v>
+        <v>0.0625</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -916,22 +939,22 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-146</v>
+        <v>-144</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.666</v>
+        <v>0.648</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.5935</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0725</v>
+        <v>0.0578</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -76,22 +76,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EAD6F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F4FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -588,14 +588,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — March 31, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 01, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  5 overs  |  2 unders  |  9.0 recommended units at risk</t>
+          <t>18 bets today  |  8 overs  |  10 unders  |  23.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -659,146 +659,146 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-102</v>
+        <v>116</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.707</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.505</v>
+        <v>0.463</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.178</v>
+        <v>0.244</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-108</v>
+        <v>116</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.672</v>
+        <v>0.644</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.463</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1528</v>
+        <v>0.181</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F6" s="17" t="n">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.66</v>
+        <v>0.724</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.5455</v>
+        <v>0.5556</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.1145</v>
+        <v>0.1684</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K6" s="21" t="n">
-        <v>0.63</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D7" s="24" t="n">
@@ -806,155 +806,628 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F7" s="23" t="n">
-        <v>116</v>
+        <v>-102</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.668</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0.463</v>
+        <v>0.505</v>
       </c>
       <c r="I7" s="26" t="n">
-        <v>0.103</v>
+        <v>0.163</v>
       </c>
       <c r="J7" s="24" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K7" s="27" t="n">
-        <v>0.48</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>124</v>
+        <v>-136</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.525</v>
+        <v>0.732</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.0786</v>
+        <v>0.5763</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1557</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.35</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>-146</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>106</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="I11" s="26" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-132</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-172</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>-178</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>104</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D19" s="12" t="n">
         <v>3.5</v>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="J9" s="12" t="n">
+      <c r="F20" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="J20" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="15" t="n">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Aaron Civale</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-144</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.0578</v>
-      </c>
-      <c r="J10" s="6" t="n">
+      <c r="K20" s="21" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="9" t="n">
-        <v>0.35</v>
+      <c r="K21" s="15" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18 bets today  |  8 overs  |  10 unders  |  23.0 recommended units at risk</t>
+          <t>20 bets today  |  10 overs  |  10 unders  |  25.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="F11" s="23" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>0.624</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>0.4854</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="26" t="n">
-        <v>0.1386</v>
+        <v>0.124</v>
       </c>
       <c r="J11" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="K11" s="27" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-132</v>
+        <v>-138</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0.696</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.569</v>
+        <v>0.5798</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.127</v>
+        <v>0.1162</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -1175,17 +1175,17 @@
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="F16" s="17" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>0.4902</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>0.0708</v>
+        <v>0.076</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1240,85 +1240,85 @@
         </is>
       </c>
       <c r="F17" s="23" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" s="25" t="n">
         <v>0.57</v>
       </c>
       <c r="H17" s="25" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>104</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="J18" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="I17" s="25" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K17" s="27" t="n">
+      <c r="K18" s="21" t="n">
         <v>0.35</v>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>0.0692</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>0.33</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
@@ -1326,108 +1326,194 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.525</v>
+        <v>0.55</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.4587</v>
+        <v>0.4808</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0.0663</v>
+        <v>0.0692</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" s="15" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.31</v>
       </c>
     </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Kevin Gausman</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D21" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F21" s="23" t="n">
         <v>116</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G21" s="25" t="n">
         <v>0.529</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H21" s="25" t="n">
         <v>0.463</v>
       </c>
-      <c r="I20" s="19" t="n">
+      <c r="I21" s="25" t="n">
         <v>0.066</v>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J21" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="K20" s="21" t="n">
+      <c r="K21" s="27" t="n">
         <v>0.31</v>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Yusei Kikuchi</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D22" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>104</v>
-      </c>
-      <c r="G21" s="13" t="n">
+      <c r="F22" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="G22" s="7" t="n">
         <v>0.556</v>
       </c>
-      <c r="H21" s="13" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>0.0658</v>
-      </c>
-      <c r="J21" s="12" t="n">
+      <c r="H22" s="7" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="J22" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="K21" s="15" t="n">
-        <v>0.32</v>
+      <c r="K22" s="9" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>116</v>
+      </c>
+      <c r="G23" s="25" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H23" s="25" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I23" s="25" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J23" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K23" s="27" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -81,17 +81,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20 bets today  |  10 overs  |  10 unders  |  25.0 recommended units at risk</t>
+          <t>15 bets today  |  8 overs  |  7 unders  |  17.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -681,171 +681,171 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>0.707</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.463</v>
+        <v>0.4717</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.244</v>
+        <v>0.2353</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>116</v>
+        <v>-128</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.644</v>
+        <v>0.735</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.463</v>
+        <v>0.5614</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.181</v>
+        <v>0.1736</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Adrian Houser</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.1684</v>
-      </c>
-      <c r="J6" s="18" t="n">
+      <c r="F7" s="11" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="J7" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="21" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Cade Cavalli</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>-102</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="H7" s="25" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="J7" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="27" t="n">
+      <c r="K7" s="15" t="n">
         <v>0.82</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -853,171 +853,171 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n">
         <v>-136</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H8" s="7" t="n">
+      <c r="G9" s="19" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="H9" s="19" t="n">
         <v>0.5763</v>
       </c>
-      <c r="I8" s="8" t="n">
-        <v>0.1557</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="I9" s="20" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>-172</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>0.1487</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Cam Schlittler</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>-146</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>0.1415</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="26" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="J11" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K11" s="27" t="n">
+      <c r="F11" s="17" t="n">
+        <v>-174</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="21" t="n">
         <v>0.62</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -1025,124 +1025,124 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-138</v>
+        <v>110</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.696</v>
+        <v>0.556</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>0.1162</v>
+        <v>0.4762</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0798</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Nathan Eovaldi</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Shane Smith</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F13" s="23" t="n">
-        <v>-172</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>0.1106</v>
-      </c>
-      <c r="J13" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K13" s="27" t="n">
-        <v>0.75</v>
+      <c r="F13" s="11" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Mike Burrows</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>0.1077</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>0.57</v>
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>104</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
@@ -1150,369 +1150,154 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="25" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>-178</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0.6403</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="F17" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F16" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="H16" s="19" t="n">
+      <c r="F18" s="23" t="n">
+        <v>116</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J18" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="I16" s="19" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>102</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="I17" s="25" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Noah Cameron</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>0.0708</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>108</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>0.0692</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K19" s="15" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Matthew Liberatore</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>Kevin Gausman</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>116</v>
-      </c>
-      <c r="G21" s="25" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="H21" s="25" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I21" s="25" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="J21" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K21" s="27" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>Freddy Peralta</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="n">
-        <v>116</v>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H23" s="25" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I23" s="25" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="J23" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K23" s="27" t="n">
+      <c r="K18" s="27" t="n">
         <v>0.24</v>
       </c>
     </row>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15 bets today  |  8 overs  |  7 unders  |  17.5 recommended units at risk</t>
+          <t>20 bets today  |  10 overs  |  10 unders  |  25.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -702,21 +702,21 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-128</v>
+        <v>-125</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.735</v>
+        <v>0.724</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5614</v>
+        <v>0.5556</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1736</v>
+        <v>0.1684</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -831,21 +831,21 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -853,42 +853,42 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-112</v>
+        <v>-136</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.677</v>
+        <v>0.732</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5283</v>
+        <v>0.5763</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.1487</v>
+        <v>0.1557</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
       <c r="D9" s="18" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
@@ -896,38 +896,38 @@
         </is>
       </c>
       <c r="F9" s="17" t="n">
-        <v>-136</v>
+        <v>-114</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.696</v>
+        <v>0.677</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>0.5763</v>
+        <v>0.5327</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>0.1197</v>
+        <v>0.1443</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="K9" s="21" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D10" s="24" t="n">
@@ -939,38 +939,38 @@
         </is>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-172</v>
+        <v>-146</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>0.743</v>
+        <v>0.735</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>0.6324</v>
+        <v>0.5935</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0.1106</v>
+        <v>0.1415</v>
       </c>
       <c r="J10" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="K10" s="27" t="n">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
@@ -982,128 +982,128 @@
         </is>
       </c>
       <c r="F11" s="17" t="n">
-        <v>-174</v>
+        <v>-132</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.726</v>
+        <v>0.696</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>0.091</v>
+        <v>0.569</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>0.127</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K11" s="21" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K12" s="27" t="n">
         <v>0.62</v>
       </c>
     </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.0798</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>-102</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="J13" s="12" t="n">
+      <c r="F13" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K13" s="21" t="n">
         <v>0.5</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.36</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D14" s="24" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
@@ -1111,128 +1111,128 @@
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>104</v>
+        <v>-172</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.743</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <v>0.0708</v>
+        <v>0.6324</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>0.1106</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Kevin Gausman</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>118</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>0.0703</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>Kyle Freeland</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="25" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.35</v>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-178</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Yusei Kikuchi</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
@@ -1240,42 +1240,42 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>0.525</v>
+        <v>0.556</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>0.4587</v>
+        <v>0.4762</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>0.0663</v>
+        <v>0.0798</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D18" s="24" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
@@ -1283,21 +1283,236 @@
         </is>
       </c>
       <c r="F18" s="23" t="n">
-        <v>116</v>
+        <v>-102</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.515</v>
+        <v>0.576</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>0.463</v>
+        <v>0.505</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>0.052</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J18" s="24" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" s="27" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>118</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Matthew Liberatore</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>116</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K23" s="15" t="n">
         <v>0.24</v>
       </c>
     </row>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18 bets today  |  9 overs  |  9 unders  |  23.5 recommended units at risk</t>
+          <t>19 bets today  |  9 overs  |  10 unders  |  25.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -896,128 +896,128 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>0.677</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.1532</v>
+        <v>0.1487</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Cam Schlittler</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Paul Skenes</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D11" s="12" t="n">
         <v>7.5</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>-132</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.696</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.569</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I11" s="14" t="n">
         <v>0.127</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J11" s="12" t="n">
         <v>1.5</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K11" s="15" t="n">
         <v>0.74</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="26" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="J11" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>0.62</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
@@ -1025,81 +1025,81 @@
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>-168</v>
+        <v>100</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.743</v>
+        <v>0.624</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>0.6269</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>0.1161</v>
+        <v>0.124</v>
       </c>
       <c r="J12" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="K12" s="21" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Nathan Eovaldi</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-168</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K13" s="27" t="n">
         <v>0.78</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>128</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>0.1114</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
@@ -1111,128 +1111,128 @@
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-114</v>
+        <v>128</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.636</v>
+        <v>0.55</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.5327</v>
+        <v>0.4386</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.1033</v>
+        <v>0.1114</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K14" s="9" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Mike Burrows</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K15" s="15" t="n">
         <v>0.55</v>
       </c>
     </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Shane Smith</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="J15" s="24" t="n">
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-178</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="27" t="n">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Noah Cameron</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>0.0708</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>0.35</v>
+      <c r="K16" s="9" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Shane Smith</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D17" s="24" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
@@ -1243,190 +1243,233 @@
         <v>100</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>0.57</v>
+        <v>0.576</v>
       </c>
       <c r="H17" s="25" t="n">
         <v>0.5</v>
       </c>
       <c r="I17" s="25" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J17" s="24" t="n">
+      <c r="J18" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K17" s="27" t="n">
+      <c r="K18" s="21" t="n">
         <v>0.35</v>
       </c>
     </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Matthew Liberatore</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D19" s="12" t="n">
         <v>3.5</v>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F19" s="11" t="n">
         <v>118</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G19" s="13" t="n">
         <v>0.525</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.4587</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.0663</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J19" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K19" s="15" t="n">
         <v>0.31</v>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Kevin Gausman</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D20" s="18" t="n">
         <v>7.5</v>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F20" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G20" s="19" t="n">
         <v>0.529</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H20" s="19" t="n">
         <v>0.463</v>
       </c>
-      <c r="I19" s="25" t="n">
+      <c r="I20" s="19" t="n">
         <v>0.066</v>
       </c>
-      <c r="J19" s="24" t="n">
+      <c r="J20" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K19" s="27" t="n">
+      <c r="K20" s="21" t="n">
         <v>0.31</v>
       </c>
     </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Yusei Kikuchi</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>CHC</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D21" s="12" t="n">
         <v>4.5</v>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F21" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.556</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.495</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.061</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J21" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K21" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Freddy Peralta</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D22" s="18" t="n">
         <v>6.5</v>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F22" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G22" s="19" t="n">
         <v>0.515</v>
       </c>
-      <c r="H21" s="25" t="n">
+      <c r="H22" s="19" t="n">
         <v>0.463</v>
       </c>
-      <c r="I21" s="25" t="n">
+      <c r="I22" s="19" t="n">
         <v>0.052</v>
       </c>
-      <c r="J21" s="24" t="n">
+      <c r="J22" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K21" s="27" t="n">
+      <c r="K22" s="21" t="n">
         <v>0.24</v>
       </c>
     </row>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>0.868</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4587</v>
+        <v>0.463</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.4093</v>
+        <v>0.405</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>118</v>
+        <v>-152</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.722</v>
+        <v>0.821</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4587</v>
+        <v>0.6032</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.2633</v>
+        <v>0.2178</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -76,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -549,7 +549,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2 bets today  |  1 overs  |  1 unders  |  4.0 recommended units at risk</t>
+          <t>2 bets today  |  1 overs  |  1 unders  |  3.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -613,87 +613,87 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Cole Ragans</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>116</v>
+        <v>-152</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.868</v>
+        <v>0.738</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.463</v>
+        <v>0.6032</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.405</v>
+        <v>0.1348</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.89</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Cole Ragans</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-152</v>
+        <v>118</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.821</v>
+        <v>0.573</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.6032</v>
+        <v>0.4587</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.2178</v>
+        <v>0.1143</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>1.37</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +82,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -156,6 +161,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -542,14 +562,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 02, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 03, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2 bets today  |  1 overs  |  1 unders  |  3.0 recommended units at risk</t>
+          <t>7 bets today  |  2 overs  |  5 unders  |  6.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -613,21 +633,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Cole Ragans</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -635,33 +655,33 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-152</v>
+        <v>108</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.738</v>
+        <v>0.722</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.6032</v>
+        <v>0.4808</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1348</v>
+        <v>0.2412</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.85</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -670,7 +690,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -678,22 +698,237 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>118</v>
+        <v>-138</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.573</v>
+        <v>0.68</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4587</v>
+        <v>0.5798</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1143</v>
+        <v>0.1002</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Michael King</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Michael McGreevy</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Framber Valdez</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Will Warren</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-174</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Mitch Keller</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,6 +87,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -157,9 +162,6 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -176,6 +178,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -569,7 +586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  2 overs  |  5 unders  |  6.5 recommended units at risk</t>
+          <t>7 bets today  |  4 overs  |  3 unders  |  6.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -633,60 +650,60 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>108</v>
+        <v>-128</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.722</v>
+        <v>0.68</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4808</v>
+        <v>0.5614</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2412</v>
+        <v>0.1186</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.16</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Chad Patrick</t>
+          <t>Cade Horton</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -698,124 +715,124 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-138</v>
+        <v>-136</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.1002</v>
+        <v>0.5763</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0.0997</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Chad Patrick</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>102</v>
+        <v>-138</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.578</v>
+        <v>0.672</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.495</v>
+        <v>0.5798</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.083</v>
+        <v>0.0922</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Michael McGreevy</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>-136</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.5763</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>0.0607</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.36</v>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Michael King</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -823,111 +840,111 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-110</v>
+        <v>-146</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.583</v>
+        <v>0.659</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5238</v>
+        <v>0.5935</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0592</v>
+        <v>0.0655</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Will Warren</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Framber Valdez</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F9" s="17" t="n">
-        <v>-174</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="J9" s="18" t="n">
+      <c r="F9" s="16" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="J9" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="20" t="n">
-        <v>0.38</v>
+      <c r="K9" s="19" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Mitch Keller</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="22" t="n">
         <v>4.5</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="21" t="n">
         <v>122</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="23" t="n">
         <v>0.505</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="23" t="n">
         <v>0.4505</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="23" t="n">
         <v>0.0545</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="24" t="n">
         <v>0.25</v>
       </c>
     </row>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,6 +157,9 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -177,22 +175,10 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -579,14 +565,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 03, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 04, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  4 overs  |  3 unders  |  6.0 recommended units at risk</t>
+          <t>5 bets today  |  2 overs  |  3 unders  |  9.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -650,21 +636,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -672,171 +658,171 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-128</v>
+        <v>-132</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.68</v>
+        <v>0.753</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5614</v>
+        <v>0.569</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1186</v>
+        <v>0.184</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.68</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Cade Horton</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-136</v>
+        <v>-128</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.676</v>
+        <v>0.741</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5763</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>0.0997</v>
+        <v>0.5614</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.1796</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>0.59</v>
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-138</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.0922</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.55</v>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Jack Flaherty</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>104</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Carmen Mlodzinski</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F7" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.44</v>
+      <c r="F7" s="11" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -844,108 +830,22 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-146</v>
+        <v>-128</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.659</v>
+        <v>0.678</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.0655</v>
+        <v>0.5614</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1166</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Framber Valdez</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>0.06270000000000001</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Mitch Keller</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>122</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>0.4505</v>
-      </c>
-      <c r="I10" s="23" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -76,17 +76,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,9 +173,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -546,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -572,7 +569,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5 bets today  |  2 overs  |  3 unders  |  9.0 recommended units at risk</t>
+          <t>7 bets today  |  4 overs  |  3 unders  |  11.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -636,216 +633,302 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Jack Flaherty</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-132</v>
+        <v>116</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.753</v>
+        <v>0.653</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.569</v>
+        <v>0.463</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.184</v>
+        <v>0.19</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.07</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Steven Matz</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-128</v>
+        <v>116</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.741</v>
+        <v>0.651</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5614</v>
+        <v>0.463</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1796</v>
+        <v>0.188</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Jack Flaherty</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ryan Weathers</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>5.5</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.1628</v>
-      </c>
-      <c r="J6" s="18" t="n">
+      <c r="F6" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="21" t="n">
-        <v>0.8</v>
+      <c r="K6" s="9" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-108</v>
+        <v>-132</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.666</v>
+        <v>0.753</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.569</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>0.1468</v>
+        <v>0.184</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.76</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-128</v>
+        <v>-108</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.678</v>
+        <v>0.666</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5614</v>
+        <v>0.5192</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.1166</v>
+        <v>0.1468</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Randy Vásquez</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Chad Patrick</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,7 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00EAD6F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,7 +180,25 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -562,14 +585,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 04, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 05, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  4 overs  |  3 unders  |  11.5 recommended units at risk</t>
+          <t>8 bets today  |  5 overs  |  3 unders  |  8.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -633,50 +656,50 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.653</v>
+        <v>0.588</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.463</v>
+        <v>0.4545</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.19</v>
+        <v>0.1335</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Steven Matz</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -698,81 +721,81 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.651</v>
+        <v>0.575</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.463</v>
+        <v>0.4587</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.188</v>
+        <v>0.1163</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Ryan Weathers</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Logan Webb</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
         <v>5.5</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.1854</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>1.04</v>
+      <c r="F6" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Taijuan Walker</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -784,151 +807,194 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-132</v>
+        <v>-106</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.753</v>
+        <v>0.6</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0.184</v>
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0.0854</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Carmen Mlodzinski</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Luis Castillo</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>-108</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0.1468</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.76</v>
+      <c r="F8" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Randy Vásquez</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>0.1128</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.65</v>
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-146</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="26" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F10" s="17" t="n">
-        <v>-154</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>0.0717</v>
-      </c>
-      <c r="J10" s="18" t="n">
+      <c r="F10" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="20" t="n">
-        <v>0.46</v>
+      <c r="K10" s="9" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Simeon Woods Richardson</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,9 +162,6 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -178,9 +175,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -566,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -592,7 +586,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>8 bets today  |  5 overs  |  3 unders  |  8.0 recommended units at risk</t>
+          <t>7 bets today  |  5 overs  |  2 unders  |  6.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -656,17 +650,17 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -681,35 +675,35 @@
         <v>120</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.588</v>
+        <v>0.575</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0.4545</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1335</v>
+        <v>0.1205</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -721,214 +715,214 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.575</v>
+        <v>0.588</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.1163</v>
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0.08799999999999999</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.54</v>
+        <v>1</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Logan Webb</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>118</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.1003</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>0.46</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Taijuan Walker</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Taijuan Walker</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>0.0854</v>
-      </c>
-      <c r="J7" s="12" t="n">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Luis Castillo</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="J7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="15" t="n">
-        <v>0.44</v>
+      <c r="K7" s="19" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Luis Castillo</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Jack Leiter</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n">
-        <v>126</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>0.0755</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.34</v>
+      <c r="F8" s="21" t="n">
+        <v>-146</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="24" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>-146</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="H9" s="25" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="I9" s="25" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="J9" s="24" t="n">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Keider Montero</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>108</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="J9" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="26" t="n">
-        <v>0.4</v>
+      <c r="K9" s="14" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Simeon Woods Richardson</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -936,64 +930,21 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-112</v>
+        <v>106</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.591</v>
+        <v>0.547</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.5283</v>
+        <v>0.4854</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0616</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0.4854</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0.0616</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,12 +86,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -178,21 +173,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -579,14 +559,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 05, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 06, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  5 overs  |  2 unders  |  6.0 recommended units at risk</t>
+          <t>3 bets today  |  2 overs  |  1 unders  |  4.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -650,60 +630,60 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>120</v>
+        <v>-132</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.575</v>
+        <v>0.72</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4545</v>
+        <v>0.569</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1205</v>
+        <v>0.151</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.55</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -715,237 +695,65 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>100</v>
+        <v>-160</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.588</v>
+        <v>0.708</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Taijuan Walker</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.0854</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="F6" s="16" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="J6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Luis Castillo</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>128</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0.0794</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Jack Leiter</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-146</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K8" s="24" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Keider Montero</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>108</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0.06519999999999999</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.4854</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.0616</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0.3</v>
+      <c r="K6" s="19" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-160</v>
+        <v>-162</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>0.708</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6183</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.0926</v>
+        <v>0.0897</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAD6F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -157,6 +162,9 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -172,7 +180,25 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -540,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -559,14 +585,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 06, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 07, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3 bets today  |  2 overs  |  1 unders  |  4.0 recommended units at risk</t>
+          <t>12 bets today  |  2 overs  |  10 unders  |  13.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -630,21 +656,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -652,108 +678,495 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-132</v>
+        <v>122</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.72</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.569</v>
+        <v>0.4505</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.151</v>
+        <v>0.2385</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Taj Bradley</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
+      <c r="D6" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F7" s="17" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Kevin Gausman</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Nick Pivetta</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>116</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Cade Cavalli</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>-162</v>
       </c>
-      <c r="G5" s="13" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="H5" s="13" t="n">
+      <c r="G13" s="13" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>0.6183</v>
       </c>
-      <c r="I5" s="13" t="n">
-        <v>0.0897</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
+      <c r="I13" s="13" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Javier Assad</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n">
         <v>3.5</v>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="16" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>0.5283</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="J6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.45</v>
+      <c r="F14" s="23" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Garrett Crochet</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -81,17 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -180,25 +175,7 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -592,7 +569,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12 bets today  |  2 overs  |  10 unders  |  13.5 recommended units at risk</t>
+          <t>9 bets today  |  2 overs  |  7 unders  |  9.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -656,21 +633,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -678,81 +655,81 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>122</v>
+        <v>-110</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4505</v>
+        <v>0.5238</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2385</v>
+        <v>0.1772</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-108</v>
+        <v>-114</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.701</v>
+        <v>0.644</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5327</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1818</v>
+        <v>0.1113</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -764,85 +741,85 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.597</v>
+        <v>0.501</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.4762</v>
+        <v>0.3937</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.1208</v>
+        <v>0.1073</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D7" s="18" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F7" s="17" t="n">
-        <v>-114</v>
+        <v>-125</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.644</v>
+        <v>0.647</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <v>0.1113</v>
+        <v>0.5556</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>0.0914</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -850,81 +827,81 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>152</v>
+        <v>-104</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.501</v>
+        <v>0.599</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.3968</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0.1042</v>
+        <v>0.5098</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0892</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
         <v>6.5</v>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="J9" s="12" t="n">
+      <c r="F9" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="15" t="n">
-        <v>0.51</v>
+      <c r="K9" s="20" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -936,85 +913,85 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-104</v>
+        <v>-112</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.599</v>
+        <v>0.602</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.5098</v>
+        <v>0.5283</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0892</v>
+        <v>0.0737</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Javier Assad</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>116</v>
+        <v>-108</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.539</v>
+        <v>0.582</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.463</v>
+        <v>0.5192</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>0.076</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -1022,150 +999,21 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.602</v>
+        <v>0.594</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.5283</v>
+        <v>0.5413</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.0737</v>
+        <v>0.0527</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Andrew Abbott</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>-162</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0.6183</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0.0687</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>Javier Assad</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>-108</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <v>0.06279999999999999</v>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Garrett Crochet</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>-118</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>0.0527</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K15" s="15" t="n">
         <v>0.29</v>
       </c>
     </row>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAD6F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -161,21 +156,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -562,14 +542,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 07, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 08, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>9 bets today  |  2 overs  |  7 unders  |  9.5 recommended units at risk</t>
+          <t>7 bets today  |  0 overs  |  7 unders  |  8.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -633,21 +613,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -655,81 +635,81 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-110</v>
+        <v>110</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.701</v>
+        <v>0.649</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1772</v>
+        <v>0.1728</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Grant Holmes</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-114</v>
+        <v>-138</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.644</v>
+        <v>0.712</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5327</v>
+        <v>0.5798</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1113</v>
+        <v>0.1322</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -741,81 +721,81 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>154</v>
+        <v>-102</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.501</v>
+        <v>0.63</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.3937</v>
+        <v>0.505</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.1073</v>
+        <v>0.125</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Nick Pivetta</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="n">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Dylan Cease</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>6.5</v>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I7" s="19" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="20" t="n">
-        <v>0.51</v>
+      <c r="F7" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -827,85 +807,85 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-104</v>
+        <v>-125</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.599</v>
+        <v>0.634</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5098</v>
+        <v>0.5556</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0892</v>
+        <v>0.0784</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Joey Cantillo</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F9" s="17" t="n">
-        <v>116</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0.35</v>
+      <c r="F9" s="11" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Eury Pérez</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -913,108 +893,22 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-112</v>
+        <v>-132</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.602</v>
+        <v>0.635</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.5283</v>
+        <v>0.569</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0737</v>
+        <v>0.066</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Javier Assad</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>-108</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0.06279999999999999</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Garrett Crochet</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-118</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.0527</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +76,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -156,6 +166,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -549,7 +592,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  0 overs  |  7 unders  |  8.5 recommended units at risk</t>
+          <t>10 bets today  |  4 overs  |  6 unders  |  9.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -613,64 +656,64 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.649</v>
+        <v>0.674</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4762</v>
+        <v>0.4673</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1728</v>
+        <v>0.2067</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Grant Holmes</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -678,85 +721,85 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-138</v>
+        <v>110</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.712</v>
+        <v>0.649</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5798</v>
+        <v>0.4762</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1322</v>
+        <v>0.1728</v>
       </c>
       <c r="J5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Michael King</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J6" s="18" t="n">
         <v>1.5</v>
       </c>
-      <c r="K5" s="15" t="n">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-102</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="21" t="n">
         <v>0.63</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -764,38 +807,38 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>128</v>
+        <v>-125</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.546</v>
+        <v>0.634</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0.1074</v>
+        <v>0.5556</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0.0784</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -803,26 +846,26 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-125</v>
+        <v>124</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.634</v>
+        <v>0.521</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5556</v>
+        <v>0.4464</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0784</v>
+        <v>0.0746</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -869,46 +912,175 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Dylan Cease</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0.0698</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Eury Pérez</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D11" s="12" t="n">
         <v>6.5</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="11" t="n">
         <v>-132</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.635</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.569</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.066</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J11" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K11" s="15" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Michael Lorenzen</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Michael McGreevy</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="26" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,12 +86,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,9 +157,6 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -180,25 +172,7 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -585,14 +559,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 08, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 09, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10 bets today  |  4 overs  |  6 unders  |  9.5 recommended units at risk</t>
+          <t>3 bets today  |  1 overs  |  2 unders  |  2.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -656,60 +630,60 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Max Meyer</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>114</v>
+        <v>-102</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.674</v>
+        <v>0.653</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4673</v>
+        <v>0.505</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2067</v>
+        <v>0.148</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Jack Flaherty</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -721,366 +695,65 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.649</v>
+        <v>0.542</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.1728</v>
+        <v>0.4717</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0.0703</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Nolan McLean</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
         <v>5.5</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>-102</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Tyler Mahle</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="n">
         <v>-125</v>
       </c>
-      <c r="G7" s="13" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="H7" s="13" t="n">
+      <c r="G6" s="18" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="H6" s="18" t="n">
         <v>0.5556</v>
       </c>
-      <c r="I7" s="13" t="n">
-        <v>0.0784</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Cristian Javier</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.0746</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="I6" s="18" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="J6" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="9" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Joey Cantillo</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>-154</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0.0727</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Dylan Cease</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>110</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>0.0698</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="21" t="n">
+      <c r="K6" s="19" t="n">
         <v>0.33</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Eury Pérez</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>-132</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Michael Lorenzen</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.0648</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Michael McGreevy</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I13" s="25" t="n">
-        <v>0.0533</v>
-      </c>
-      <c r="J13" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K13" s="26" t="n">
-        <v>0.29</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,14 +50,8 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001A7431"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,12 +75,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -139,9 +128,6 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -158,21 +144,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -540,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -566,7 +537,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3 bets today  |  1 overs  |  2 unders  |  2.5 recommended units at risk</t>
+          <t>2 bets today  |  1 overs  |  1 unders  |  1.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -630,17 +601,17 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Max Meyer</t>
+          <t>Jack Flaherty</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -652,108 +623,65 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-102</v>
+        <v>112</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.653</v>
+        <v>0.542</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>0.148</v>
+        <v>0.4717</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.0703</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Jack Flaherty</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Nolan McLean</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>5.5</v>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>112</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0.4717</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>0.0703</v>
-      </c>
-      <c r="J5" s="12" t="n">
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="J5" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="K5" s="14" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Nolan McLean</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>0.0594</v>
-      </c>
-      <c r="J6" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.33</v>
+      <c r="K5" s="13" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +50,14 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A7431"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +76,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,6 +144,9 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -143,7 +162,46 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -511,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -530,14 +588,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 09, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 10, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2 bets today  |  1 overs  |  1 unders  |  1.0 recommended units at risk</t>
+          <t>9 bets today  |  5 overs  |  4 unders  |  11.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -601,87 +659,388 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Steven Matz</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0.1808</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Shota Imanaga</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Bryce Elder</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1218</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Simeon Woods Richardson</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Shane Baz</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>0.4717</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0.0703</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="F8" s="23" t="n">
+        <v>-132</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="J8" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Jake Irvin</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Kris Bubic</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K4" s="8" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Nolan McLean</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.5495</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="J5" s="11" t="n">
+      <c r="K11" s="15" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Chad Patrick</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>110</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="J12" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="K5" s="13" t="n">
-        <v>0.36</v>
+      <c r="K12" s="27" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -595,7 +595,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>9 bets today  |  5 overs  |  4 unders  |  11.5 recommended units at risk</t>
+          <t>9 bets today  |  5 overs  |  4 unders  |  12.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -724,22 +724,22 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>0.652</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4902</v>
+        <v>0.4762</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1618</v>
+        <v>0.1758</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -915,89 +915,89 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Kris Bubic</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>102</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="I10" s="25" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Jake Irvin</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D11" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="17" t="n">
         <v>124</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.522</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H11" s="19" t="n">
         <v>0.4464</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I11" s="19" t="n">
         <v>0.0756</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K11" s="21" t="n">
         <v>0.34</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Kris Bubic</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0.0563</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>0.3</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="F12" s="23" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G12" s="25" t="n">
         <v>0.532</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>0.4762</v>
+        <v>0.4808</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>0.0558</v>
+        <v>0.0512</v>
       </c>
       <c r="J12" s="24" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" s="27" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -180,9 +180,6 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -196,9 +193,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -588,14 +582,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 10, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 11, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>9 bets today  |  5 overs  |  4 unders  |  12.0 recommended units at risk</t>
+          <t>4 bets today  |  2 overs  |  2 unders  |  4.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -659,60 +653,60 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Steven Matz</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>104</v>
+        <v>-154</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.671</v>
+        <v>0.736</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4902</v>
+        <v>0.6063</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1808</v>
+        <v>0.1297</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Kyle Harrison</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -724,323 +718,108 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.652</v>
+        <v>0.615</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4762</v>
+        <v>0.495</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1758</v>
+        <v>0.12</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.84</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Bryce Elder</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Casey Mize</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.1218</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.58</v>
+      <c r="F6" s="17" t="n">
+        <v>114</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Simeon Woods Richardson</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Jacob Lopez</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="22" t="n">
         <v>-154</v>
       </c>
-      <c r="G7" s="19" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="H7" s="19" t="n">
+      <c r="G7" s="24" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="H7" s="24" t="n">
         <v>0.6063</v>
       </c>
-      <c r="I7" s="20" t="n">
-        <v>0.1177</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>Shane Baz</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>-132</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I8" s="26" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="J8" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>-118</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.0997</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="21" t="n">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>Kris Bubic</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>102</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="I10" s="25" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J10" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="27" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Jake Irvin</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>124</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>0.0756</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>Chad Patrick</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>108</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>0.0512</v>
-      </c>
-      <c r="J12" s="24" t="n">
+      <c r="I7" s="24" t="n">
+        <v>0.0677</v>
+      </c>
+      <c r="J7" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="K12" s="27" t="n">
-        <v>0.25</v>
+      <c r="K7" s="25" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -582,14 +582,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 11, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 12, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>4 bets today  |  2 overs  |  2 unders  |  4.5 recommended units at risk</t>
+          <t>12 bets today  |  3 overs  |  9 unders  |  14.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -675,151 +675,495 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-154</v>
+        <v>102</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.736</v>
+        <v>0.721</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.6063</v>
+        <v>0.495</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1297</v>
+        <v>0.226</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Kyle Harrison</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>-140</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.2217</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Andrew Abbott</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-168</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1941</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Chris Sale</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>108</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1123</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Cade Povich</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Logan Gilbert</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-148</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.5968</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Adrian Houser</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Brandon Woodruff</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D12" s="6" t="n">
         <v>5.5</v>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>102</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Casey Mize</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="F12" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Jacob deGrom</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>122</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Kyle Freeland</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Sandy Alcantara</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="D15" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>114</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="I6" s="19" t="n">
-        <v>0.09470000000000001</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Jacob Lopez</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>-154</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="H7" s="24" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="I7" s="24" t="n">
-        <v>0.0677</v>
-      </c>
-      <c r="J7" s="23" t="n">
+      <c r="F15" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="J15" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="25" t="n">
-        <v>0.43</v>
+      <c r="K15" s="20" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +45,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A7431"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +72,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD6F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -96,6 +125,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -482,14 +565,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MLB Strikeout Prop Bets — </t>
+          <t>MLB Strikeout Prop Bets — April 14, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>0 bets today  |  0 overs  |  0 unders  |  0.0 recommended units at risk</t>
+          <t>10 bets today  |  3 overs  |  7 unders  |  11.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -548,6 +631,436 @@
         <is>
           <t>Kelly Units</t>
         </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Yoshinobu Yamamoto</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Michael Lorenzen</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Jeffrey Springs</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>OAK</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ryan Weathers</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Michael King</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Nolan McLean</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>-148</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.5968</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Sonny Gray</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Michael McGreevy</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
         <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -179,6 +184,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -565,14 +585,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 14, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 15, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10 bets today  |  3 overs  |  7 unders  |  11.5 recommended units at risk</t>
+          <t>11 bets today  |  7 overs  |  4 unders  |  13.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -636,7 +656,7 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -658,38 +678,38 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-122</v>
+        <v>118</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.729</v>
+        <v>0.724</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5495</v>
+        <v>0.4587</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1795</v>
+        <v>0.2653</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Jack Kochanowicz</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -701,42 +721,42 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-104</v>
+        <v>116</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.68</v>
+        <v>0.633</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5098</v>
+        <v>0.463</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1702</v>
+        <v>0.17</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Spencer Arrighetti</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -744,42 +764,42 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-138</v>
+        <v>-132</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.721</v>
+        <v>0.738</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.5798</v>
+        <v>0.569</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.1412</v>
+        <v>0.169</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Luis Gil</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D7" s="18" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
@@ -787,38 +807,38 @@
         </is>
       </c>
       <c r="F7" s="17" t="n">
-        <v>-102</v>
+        <v>-114</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.633</v>
+        <v>0.653</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.505</v>
+        <v>0.5327</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.128</v>
+        <v>0.1203</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="K7" s="21" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -830,128 +850,128 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>110</v>
+        <v>-114</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.6</v>
+        <v>0.642</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.4762</v>
+        <v>0.5327</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.1238</v>
+        <v>0.1093</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.0924</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="21" t="n">
-        <v>0.52</v>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Jake Irvin</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Kyle Bradish</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.5495</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.0745</v>
-      </c>
-      <c r="J10" s="6" t="n">
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="I10" s="25" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="J10" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="9" t="n">
-        <v>0.41</v>
+      <c r="K10" s="26" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
@@ -959,71 +979,71 @@
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>-148</v>
+        <v>118</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.669</v>
+        <v>0.525</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.4587</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>0.0722</v>
+        <v>0.0663</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Sonny Gray</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J12" s="6" t="n">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Slade Cecconi</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>130</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="J12" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="K12" s="9" t="n">
-        <v>0.29</v>
+      <c r="K12" s="26" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -1045,22 +1065,65 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>136</v>
+        <v>-144</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.482</v>
+        <v>0.642</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.4237</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>0.0583</v>
+        <v>0.0518</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Clay Holmes</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,22 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,43 +152,7 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -585,14 +539,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 15, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 16, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11 bets today  |  7 overs  |  4 unders  |  13.0 recommended units at risk</t>
+          <t>3 bets today  |  2 overs  |  1 unders  |  3.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -656,474 +610,130 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Steven Matz</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.724</v>
+        <v>0.622</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4587</v>
+        <v>0.4348</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2653</v>
+        <v>0.1872</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Jack Kochanowicz</t>
+          <t>Max Fried</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>116</v>
+        <v>-132</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.633</v>
+        <v>0.664</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.17</v>
+        <v>0.569</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0.095</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.79</v>
+        <v>1</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Spencer Arrighetti</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
         <v>-132</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.738</v>
+        <v>0.63</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0.569</v>
       </c>
-      <c r="I6" s="8" t="n">
-        <v>0.169</v>
+      <c r="I6" s="7" t="n">
+        <v>0.061</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Luis Gil</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <v>0.1203</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Shota Imanaga</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0.1093</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Jake Irvin</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>126</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.4425</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>0.1075</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>Kyle Bradish</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>-104</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <v>0.5098</v>
-      </c>
-      <c r="I10" s="25" t="n">
-        <v>0.0722</v>
-      </c>
-      <c r="J10" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="26" t="n">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Randy Vásquez</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>118</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0.0663</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>Slade Cecconi</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>130</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>0.4348</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>0.0622</v>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="26" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>-144</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>Clay Holmes</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>-154</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <v>0.0517</v>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +76,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EAD6F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,7 +162,46 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -520,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -539,14 +588,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 16, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 17, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3 bets today  |  2 overs  |  1 unders  |  3.5 recommended units at risk</t>
+          <t>13 bets today  |  7 overs  |  6 unders  |  17.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -610,130 +659,560 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Steven Matz</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.622</v>
+        <v>0.662</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4348</v>
+        <v>0.4464</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1872</v>
+        <v>0.2156</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Max Fried</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Eric Lauer</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Logan Gilbert</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Edward Cabrera</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Tyler Glasnow</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Michael Wacha</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="D10" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Tomoyuki Sugano</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>116</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I11" s="26" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Zack Littell</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Ranger Suarez</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>-132</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Parker Messick</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="F13" s="11" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Chris Bassitt</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="D15" s="24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>-132</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="F15" s="23" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="J15" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>0.35</v>
+      <c r="K15" s="27" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Martín Pérez</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>114</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -81,17 +81,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -180,9 +180,6 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -196,9 +193,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -588,14 +582,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 17, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 18, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>13 bets today  |  7 overs  |  6 unders  |  17.5 recommended units at risk</t>
+          <t>14 bets today  |  6 overs  |  8 unders  |  14.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -659,21 +653,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -681,171 +675,171 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>124</v>
+        <v>-118</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.662</v>
+        <v>0.729</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4464</v>
+        <v>0.5413</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2156</v>
+        <v>0.1877</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>102</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>104</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.1748</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Eric Lauer</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="5" t="n">
         <v>-136</v>
       </c>
-      <c r="G6" s="19" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="H6" s="19" t="n">
+      <c r="G6" s="7" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <v>0.5763</v>
       </c>
-      <c r="I6" s="20" t="n">
-        <v>0.1727</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>1.02</v>
+      <c r="I6" s="8" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-122</v>
+        <v>124</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.712</v>
+        <v>0.578</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.5495</v>
+        <v>0.4464</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>0.1625</v>
+        <v>0.1316</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -853,366 +847,409 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Brayan Bello</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Cristopher Sánchez</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Gavin Williams</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Germán Márquez</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="n">
         <v>-104</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H8" s="7" t="n">
+      <c r="G12" s="24" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="H12" s="24" t="n">
         <v>0.5098</v>
       </c>
-      <c r="I8" s="8" t="n">
-        <v>0.1502</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Tyler Glasnow</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.5495</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>0.1275</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Michael Wacha</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>0.1073</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Tomoyuki Sugano</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>116</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I11" s="26" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="J11" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Zack Littell</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>134</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0.4274</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>0.08359999999999999</v>
-      </c>
-      <c r="J12" s="18" t="n">
+      <c r="I12" s="24" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="J12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="21" t="n">
-        <v>0.37</v>
+      <c r="K12" s="25" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Ranger Suarez</t>
+          <t>Brandon Woodruff</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>-104</v>
+        <v>120</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.581</v>
+        <v>0.528</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.5098</v>
+        <v>0.4545</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>0.0712</v>
+        <v>0.0735</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>118</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F16" s="22" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Lance McCullers Jr.</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="n">
         <v>118</v>
       </c>
-      <c r="G14" s="19" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="H14" s="19" t="n">
+      <c r="G17" s="19" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="H17" s="19" t="n">
         <v>0.4587</v>
       </c>
-      <c r="I14" s="19" t="n">
-        <v>0.0703</v>
-      </c>
-      <c r="J14" s="18" t="n">
+      <c r="I17" s="19" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="J17" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="21" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Chris Bassitt</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>0.0598</v>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Martín Pérez</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>114</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>0.0567</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>0.27</v>
+      <c r="K17" s="20" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -180,6 +180,9 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -193,6 +196,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -589,7 +595,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>14 bets today  |  6 overs  |  8 unders  |  14.5 recommended units at risk</t>
+          <t>14 bets today  |  6 overs  |  8 unders  |  16.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -675,22 +681,22 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-118</v>
+        <v>-112</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5413</v>
+        <v>0.5283</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1877</v>
+        <v>0.2017</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -721,105 +727,105 @@
         <v>102</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.63</v>
+        <v>0.648</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>0.495</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.135</v>
+        <v>0.153</v>
       </c>
       <c r="J5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Max Scherzer</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>-140</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="J7" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="K5" s="15" t="n">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Paul Skenes</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-136</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.5763</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.1327</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>124</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0.1316</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.59</v>
+      <c r="K7" s="27" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -847,85 +853,85 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>0.639</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.1198</v>
+        <v>0.1152</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Brayan Bello</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="J9" s="18" t="n">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Brandon Woodruff</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>132</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="20" t="n">
-        <v>0.5600000000000001</v>
+      <c r="K9" s="15" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Brayan Bello</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -933,128 +939,128 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-154</v>
+        <v>-130</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.661</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.6063</v>
+        <v>0.5652</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0837</v>
+        <v>0.0958</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Cristopher Sánchez</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Gavin Williams</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D12" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n">
-        <v>110</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>0.0828</v>
-      </c>
-      <c r="J11" s="18" t="n">
+      <c r="F12" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="20" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Germán Márquez</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>-104</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>0.5098</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>0.07820000000000001</v>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="25" t="n">
-        <v>0.4</v>
+      <c r="K12" s="9" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Brandon Woodruff</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1062,194 +1068,194 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.528</v>
+        <v>0.518</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.4386</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>0.0735</v>
+        <v>0.0794</v>
       </c>
       <c r="J13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Germán Márquez</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Yusei Kikuchi</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>110</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="J15" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="15" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="K15" s="27" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Lance McCullers Jr.</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="D16" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Noah Cameron</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F14" s="22" t="n">
-        <v>118</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I14" s="24" t="n">
-        <v>0.0603</v>
-      </c>
-      <c r="J14" s="23" t="n">
+      <c r="F17" s="11" t="n">
+        <v>-132</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="25" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="n">
-        <v>110</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>0.0568</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>Noah Cameron</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>0.0548</v>
-      </c>
-      <c r="J16" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Lance McCullers Jr.</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>118</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>0.0523</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>0.24</v>
+      <c r="K17" s="15" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -76,22 +76,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F4FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -180,9 +180,6 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -196,9 +193,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -588,14 +582,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 18, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 19, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>14 bets today  |  6 overs  |  8 unders  |  16.5 recommended units at risk</t>
+          <t>8 bets today  |  2 overs  |  6 unders  |  7.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -659,603 +653,345 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-112</v>
+        <v>-120</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.73</v>
+        <v>0.669</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5283</v>
+        <v>0.5455</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2017</v>
+        <v>0.1235</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.07</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.648</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.495</v>
+        <v>0.4464</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.153</v>
+        <v>0.1196</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F6" s="17" t="n">
-        <v>-140</v>
+        <v>-146</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.736</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.1527</v>
+        <v>0.5935</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>0.0895</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>0.92</v>
+        <v>1</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Paul Skenes</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F7" s="23" t="n">
-        <v>-138</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="H7" s="25" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>0.1462</v>
-      </c>
-      <c r="J7" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0.87</v>
+      <c r="F7" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Tarik Skubal</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Bryan Woo</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0.1152</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.6</v>
+      <c r="F8" s="17" t="n">
+        <v>-166</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0.6241</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Brandon Woodruff</t>
+          <t>Garrett Crochet</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>132</v>
+        <v>-158</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.528</v>
+        <v>0.675</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0.431</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0.097</v>
+        <v>0.0626</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Brayan Bello</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Joey Cantillo</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.661</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.5652</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.0958</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0.55</v>
+      <c r="F10" s="17" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Cristopher Sánchez</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="n">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Cole Ragans</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="n">
         <v>6.5</v>
       </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-154</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <v>0.08169999999999999</v>
-      </c>
-      <c r="J11" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Gavin Williams</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.08119999999999999</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Andre Pallante</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>128</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0.0794</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Germán Márquez</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>-104</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>0.5098</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>0.07820000000000001</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Yusei Kikuchi</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>110</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I15" s="25" t="n">
-        <v>0.0548</v>
-      </c>
-      <c r="J15" s="24" t="n">
+      <c r="F11" s="22" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="J11" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="K15" s="27" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Lance McCullers Jr.</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Noah Cameron</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>-132</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>0.3</v>
+      <c r="K11" s="25" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -82,11 +82,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,9 +157,6 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -181,21 +173,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -582,14 +559,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 19, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 20, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>8 bets today  |  2 overs  |  6 unders  |  7.0 recommended units at risk</t>
+          <t>4 bets today  |  3 overs  |  1 unders  |  4.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -653,21 +630,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -675,42 +652,42 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-120</v>
+        <v>130</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.669</v>
+        <v>0.593</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5455</v>
+        <v>0.4348</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1235</v>
+        <v>0.1582</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -718,280 +695,108 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>124</v>
+        <v>-118</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.627</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.1196</v>
+        <v>0.5413</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0.0857</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.54</v>
+        <v>1</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Jeffrey Springs</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>OAK</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>-146</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="I6" s="19" t="n">
-        <v>0.0895</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>0.55</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Kyle Bradish</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-166</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.6241</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>110</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>0.0808</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Bryan Woo</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>-166</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.6241</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>0.07489999999999999</v>
-      </c>
-      <c r="J8" s="18" t="n">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Michael McGreevy</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="J7" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="20" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Garrett Crochet</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>-158</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.6124000000000001</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0.0626</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Joey Cantillo</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>-154</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>0.0617</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>Cole Ragans</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>0.5238</v>
-      </c>
-      <c r="I11" s="24" t="n">
-        <v>0.0542</v>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="25" t="n">
-        <v>0.28</v>
+      <c r="K7" s="19" t="n">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -76,17 +76,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -157,6 +157,9 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -170,6 +173,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -540,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -559,14 +565,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 20, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 21, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>4 bets today  |  3 overs  |  1 unders  |  4.0 recommended units at risk</t>
+          <t>9 bets today  |  6 overs  |  3 unders  |  10.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -630,173 +636,388 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Kris Bubic</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>130</v>
+        <v>-138</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.593</v>
+        <v>0.719</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4348</v>
+        <v>0.5798</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1582</v>
+        <v>0.1392</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Chase Burns</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-118</v>
+        <v>-104</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.627</v>
+        <v>0.641</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>0.0857</v>
+        <v>0.5098</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.1312</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>0.47</v>
+        <v>1.5</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Parker Messick</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Steven Matz</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>122</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Jack Kochanowicz</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>116</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Sean Burke</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>-166</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.6241</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>0.07290000000000001</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="F10" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="J10" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Michael McGreevy</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="K10" s="21" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Randy Vásquez</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Chris Paddack</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>124</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0.0726</v>
-      </c>
-      <c r="J7" s="17" t="n">
+      <c r="D12" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="19" t="n">
-        <v>0.33</v>
+      <c r="K12" s="9" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAD6F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,10 +180,22 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -565,14 +582,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 21, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 22, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>9 bets today  |  6 overs  |  3 unders  |  10.0 recommended units at risk</t>
+          <t>7 bets today  |  3 overs  |  4 unders  |  7.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -636,21 +653,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Kris Bubic</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -658,38 +675,38 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-138</v>
+        <v>118</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.719</v>
+        <v>0.572</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.5798</v>
+        <v>0.4587</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1392</v>
+        <v>0.1133</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.83</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -697,46 +714,46 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-104</v>
+        <v>-158</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.641</v>
+        <v>0.721</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5098</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1312</v>
+        <v>0.1086</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Clay Holmes</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -744,280 +761,194 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-154</v>
+        <v>-112</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.728</v>
+        <v>0.636</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.6063</v>
+        <v>0.5283</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.1217</v>
+        <v>0.1077</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Parker Messick</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Braxton Ashcraft</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
         <v>5.5</v>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>0.1125</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.52</v>
+      <c r="F7" s="17" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Steven Matz</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Chris Bassitt</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n">
-        <v>122</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.4505</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>0.1025</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.47</v>
+      <c r="F8" s="22" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Jack Kochanowicz</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Eric Lauer</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="D9" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>116</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.41</v>
+      <c r="F9" s="17" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Sean Burke</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>132</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="J10" s="18" t="n">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Shohei Ohtani</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-132</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="21" t="n">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Randy Vásquez</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0.0605</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Chris Paddack</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-138</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.0572</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.34</v>
+      <c r="K10" s="9" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -81,12 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -180,6 +180,9 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -193,6 +196,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -563,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -582,14 +588,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 22, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 23, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 bets today  |  3 overs  |  4 unders  |  7.0 recommended units at risk</t>
+          <t>6 bets today  |  2 overs  |  4 unders  |  9.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -653,21 +659,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -675,38 +681,38 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.572</v>
+        <v>0.673</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4587</v>
+        <v>0.495</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1133</v>
+        <v>0.178</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.52</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
           <t>CHC</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>PHI</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -714,46 +720,46 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-158</v>
+        <v>-106</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.721</v>
+        <v>0.672</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1086</v>
+        <v>0.1574</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Clay Holmes</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -761,194 +767,151 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-112</v>
+        <v>-154</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.636</v>
+        <v>0.762</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.5283</v>
+        <v>0.6063</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.1077</v>
+        <v>0.1557</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.57</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="D7" s="18" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F7" s="17" t="n">
-        <v>-102</v>
+        <v>-174</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.596</v>
+        <v>0.758</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="I7" s="19" t="n">
-        <v>0.091</v>
+        <v>0.635</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>0.123</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="20" t="n">
-        <v>0.46</v>
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Chris Bassitt</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="n">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Davis Martin</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="n">
         <v>3.5</v>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F8" s="22" t="n">
-        <v>-118</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H8" s="24" t="n">
-        <v>0.5413</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>0.0737</v>
-      </c>
-      <c r="J8" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K8" s="25" t="n">
-        <v>0.4</v>
+      <c r="F8" s="23" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="J8" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F9" s="17" t="n">
-        <v>-120</v>
+        <v>104</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.617</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>0.5455</v>
+        <v>0.4902</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0698</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="20" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Shohei Ohtani</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-132</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0.31</v>
+      <c r="K9" s="21" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -81,17 +81,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,9 +196,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -588,14 +585,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 23, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 24, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6 bets today  |  2 overs  |  4 unders  |  9.5 recommended units at risk</t>
+          <t>11 bets today  |  5 overs  |  6 unders  |  14.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -659,17 +656,17 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -681,237 +678,452 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.673</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.495</v>
+        <v>0.4854</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.178</v>
+        <v>0.2006</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-106</v>
+        <v>-118</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.672</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5413</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1574</v>
+        <v>0.1457</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1392</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Grant Holmes</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>116</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Framber Valdez</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>-154</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.6063</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.1557</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Joe Ryan</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="F9" s="11" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Gavin Williams</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>104</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Taj Bradley</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>-174</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="I7" s="20" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>Davis Martin</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="n">
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="26" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Sandy Alcantara</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>104</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="26" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Max Scherzer</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F8" s="23" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <v>0.5495</v>
-      </c>
-      <c r="I8" s="26" t="n">
-        <v>0.1205</v>
-      </c>
-      <c r="J8" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Logan Webb</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.0698</v>
-      </c>
-      <c r="J9" s="18" t="n">
+      <c r="F14" s="17" t="n">
+        <v>-144</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="J14" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="21" t="n">
-        <v>0.34</v>
+      <c r="K14" s="21" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -81,7 +81,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3EBF9"/>
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -91,7 +91,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
+        <fgColor rgb="00F3EBF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -585,14 +585,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 24, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 25, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11 bets today  |  5 overs  |  6 unders  |  14.5 recommended units at risk</t>
+          <t>10 bets today  |  6 overs  |  4 unders  |  12.5 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -656,21 +656,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -678,124 +678,124 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>106</v>
+        <v>-154</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4854</v>
+        <v>0.6063</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2006</v>
+        <v>0.2187</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.97</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-118</v>
+        <v>-154</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.6063</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1457</v>
+        <v>0.1417</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Drew Rasmussen</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.1392</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Ryan Weathers</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="J6" s="18" t="n">
         <v>1.5</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>0.67</v>
+      <c r="K6" s="21" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Grant Holmes</t>
+          <t>Jake Irvin</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -803,46 +803,46 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.463</v>
+        <v>0.4808</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>0.131</v>
+        <v>0.1072</v>
       </c>
       <c r="J7" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Robbie Ray</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -850,38 +850,38 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-114</v>
+        <v>118</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.66</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5327</v>
+        <v>0.4587</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.1273</v>
+        <v>0.1033</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Zack Wheeler</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
@@ -889,85 +889,85 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>-106</v>
+        <v>104</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.623</v>
+        <v>0.591</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4902</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.1084</v>
+        <v>0.1008</v>
       </c>
       <c r="J9" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Gavin Williams</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>104</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>0.1048</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>0.51</v>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Brady Singer</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Jack Flaherty</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D11" s="24" t="n">
@@ -975,46 +975,46 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F11" s="23" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>0.55</v>
+        <v>0.574</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>0.4545</v>
+        <v>0.4902</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0.0955</v>
+        <v>0.0838</v>
       </c>
       <c r="J11" s="24" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="26" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Sandy Alcantara</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>OAK</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
@@ -1025,105 +1025,62 @@
         <v>138</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.508</v>
+        <v>0.485</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>0.4202</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>0.0878</v>
+        <v>0.0648</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Jameson Taillon</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="n">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Joey Cantillo</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>4.5</v>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F13" s="23" t="n">
-        <v>104</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I13" s="25" t="n">
-        <v>0.0848</v>
-      </c>
-      <c r="J13" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="26" t="n">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Max Scherzer</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>-144</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>0.5901999999999999</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>0.0568</v>
-      </c>
-      <c r="J14" s="18" t="n">
+      <c r="F13" s="11" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="21" t="n">
-        <v>0.35</v>
+      <c r="K13" s="15" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,6 +196,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -566,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -585,14 +588,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 25, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 26, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10 bets today  |  6 overs  |  4 unders  |  12.5 recommended units at risk</t>
+          <t>12 bets today  |  6 overs  |  6 unders  |  14.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -656,21 +659,21 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -678,38 +681,38 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-154</v>
+        <v>104</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.825</v>
+        <v>0.737</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.6063</v>
+        <v>0.4902</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2187</v>
+        <v>0.2468</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Ryne Nelson</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -721,214 +724,214 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-154</v>
+        <v>136</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.748</v>
+        <v>0.646</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.6063</v>
+        <v>0.4237</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1417</v>
+        <v>0.2223</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.5327</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Kyle Harrison</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>108</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="J7" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Emerson Hancock</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>110</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.1098</v>
-      </c>
-      <c r="J6" s="18" t="n">
+      <c r="F8" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="J8" s="18" t="n">
         <v>1.5</v>
       </c>
-      <c r="K6" s="21" t="n">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Jake Irvin</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="n">
+      <c r="K8" s="21" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Kodai Senga</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="n">
         <v>108</v>
       </c>
-      <c r="G7" s="13" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="H7" s="13" t="n">
+      <c r="G9" s="25" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H9" s="25" t="n">
         <v>0.4808</v>
       </c>
-      <c r="I7" s="14" t="n">
-        <v>0.1072</v>
-      </c>
-      <c r="J7" s="12" t="n">
+      <c r="I9" s="26" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="J9" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="K7" s="15" t="n">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0.1033</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Zack Wheeler</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>104</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0.4902</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>0.1008</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.49</v>
+      <c r="K9" s="27" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -936,16 +939,16 @@
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.578</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.4854</v>
+        <v>0.463</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0926</v>
+        <v>0.096</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>1</v>
@@ -957,21 +960,21 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D11" s="24" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
@@ -979,42 +982,42 @@
         </is>
       </c>
       <c r="F11" s="23" t="n">
-        <v>104</v>
+        <v>-106</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>0.574</v>
+        <v>0.587</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>0.4902</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0.0838</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="26" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Max Meyer</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>OAK</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
@@ -1022,65 +1025,151 @@
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>138</v>
+        <v>-106</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.485</v>
+        <v>0.585</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>0.4202</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>0.0648</v>
+        <v>0.0704</v>
       </c>
       <c r="J12" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Joey Cantillo</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Nolan McLean</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>NYM</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Shota Imanaga</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>114</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Keider Montero</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>CIN</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>4.5</v>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0.0553</v>
-      </c>
-      <c r="J13" s="12" t="n">
+      <c r="F15" s="11" t="n">
+        <v>112</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="15" t="n">
-        <v>0.3</v>
+      <c r="K15" s="15" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,22 +76,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD6F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -180,28 +175,7 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -569,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -588,14 +562,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 26, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 27, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12 bets today  |  6 overs  |  6 unders  |  14.0 recommended units at risk</t>
+          <t>6 bets today  |  5 overs  |  1 unders  |  7.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -659,517 +633,259 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.737</v>
+        <v>0.59</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4902</v>
+        <v>0.4202</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2468</v>
+        <v>0.1698</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Ryne Nelson</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>136</v>
+        <v>-158</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.646</v>
+        <v>0.762</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4237</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.2223</v>
+        <v>0.1496</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="15" t="n">
         <v>0.96</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Michael King</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="n">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Jack Kochanowicz</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F6" s="17" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.5327</v>
-      </c>
-      <c r="I6" s="20" t="n">
-        <v>0.1913</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>1.02</v>
+      <c r="F6" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Kyle Harrison</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>108</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="H7" s="25" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>0.1422</v>
-      </c>
-      <c r="J7" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0.68</v>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Steven Matz</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Emerson Hancock</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Chris Paddack</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n">
-        <v>120</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>0.1295</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.59</v>
+      <c r="F8" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>Kodai Senga</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>108</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H9" s="25" t="n">
-        <v>0.4808</v>
-      </c>
-      <c r="I9" s="26" t="n">
-        <v>0.1092</v>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Kyle Bradish</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Carmen Mlodzinski</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="n">
+      <c r="D9" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <v>0.07240000000000001</v>
-      </c>
-      <c r="J11" s="24" t="n">
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="J9" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K11" s="27" t="n">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Max Meyer</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>0.0704</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Nolan McLean</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>NYM</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I13" s="25" t="n">
-        <v>0.0594</v>
-      </c>
-      <c r="J13" s="24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K13" s="27" t="n">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Shota Imanaga</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>114</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>0.4673</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Keider Montero</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>CIN</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>112</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0.4717</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>0.0533</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>0.25</v>
+      <c r="K9" s="20" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="00EAD6F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,6 +87,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -176,6 +181,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -562,14 +582,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 27, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 28, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6 bets today  |  5 overs  |  1 unders  |  7.0 recommended units at risk</t>
+          <t>9 bets today  |  3 overs  |  6 unders  |  11.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -633,60 +653,60 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Chase Burns</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.59</v>
+        <v>0.637</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.4202</v>
+        <v>0.463</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1698</v>
+        <v>0.174</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -698,81 +718,81 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>-158</v>
+        <v>106</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.762</v>
+        <v>0.637</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.4854</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.1496</v>
+        <v>0.1516</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.96</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Jack Kochanowicz</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-120</v>
+        <v>-106</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.649</v>
+        <v>0.635</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.5455</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.1035</v>
+        <v>0.1204</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Steven Matz</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D7" s="18" t="n">
@@ -784,108 +804,237 @@
         </is>
       </c>
       <c r="F7" s="17" t="n">
-        <v>130</v>
+        <v>-128</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.53</v>
+        <v>0.656</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>0.4348</v>
+        <v>0.5614</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0946</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Chris Paddack</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Shane Baz</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0.0776</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Joe Ryan</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Janson Junk</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="D11" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.4464</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.06759999999999999</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="F11" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="H11" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="I11" s="19" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" s="25" t="n">
         <v>0.31</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.5495</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.0605</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0.34</v>
       </c>
     </row>
   </sheetData>

--- a/filtered_bets.xlsx
+++ b/filtered_bets.xlsx
@@ -57,7 +57,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -82,11 +82,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3EBF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,9 +157,6 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -181,21 +173,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -582,14 +559,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MLB Strikeout Prop Bets — April 28, 2026</t>
+          <t>MLB Strikeout Prop Bets — April 29, 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>9 bets today  |  3 overs  |  6 unders  |  11.0 recommended units at risk</t>
+          <t>6 bets today  |  2 overs  |  4 unders  |  6.0 recommended units at risk</t>
         </is>
       </c>
     </row>
@@ -653,17 +630,17 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -678,39 +655,39 @@
         <v>116</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.637</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0.463</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.174</v>
+        <v>0.137</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -718,171 +695,171 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>0.637</v>
+        <v>0.578</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0.4854</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.1516</v>
+        <v>0.4902</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0.0878</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.74</v>
+        <v>1</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Tanner Bibee</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Jameson Taillon</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.1204</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.62</v>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Casey Mize</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Tarik Skubal</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="D7" s="18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>-128</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.5614</v>
-      </c>
-      <c r="I7" s="19" t="n">
-        <v>0.0946</v>
-      </c>
-      <c r="J7" s="18" t="n">
+      <c r="D7" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.5798</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="J7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="20" t="n">
-        <v>0.54</v>
+      <c r="K7" s="14" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Shohei Ohtani</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>-120</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0.5455</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.0925</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Andre Pallante</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>-160</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="J8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="9" t="n">
-        <v>0.51</v>
+      <c r="K8" s="19" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Shane Baz</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -890,151 +867,22 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>106</v>
+        <v>-152</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0.4854</v>
+        <v>0.6032</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0.0776</v>
+        <v>0.0698</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Joe Ryan</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-108</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Janson Junk</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H11" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="I11" s="19" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>-138</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>0.5798</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>0.0522</v>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="25" t="n">
-        <v>0.31</v>
+      <c r="K9" s="14" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
